--- a/Result/profitability/8291.xlsx
+++ b/Result/profitability/8291.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.31</v>
+        <v>-0.33625</v>
       </c>
       <c r="N2" t="n">
-        <v>-661.7375</v>
+        <v>-500.64375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.305</v>
+        <v>-0.3175</v>
       </c>
       <c r="N3" t="n">
-        <v>-481.21875</v>
+        <v>-334.7675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.27625</v>
+        <v>-0.30875</v>
       </c>
       <c r="N4" t="n">
-        <v>-314.82125</v>
+        <v>-190.93375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.27125</v>
+        <v>-0.26375</v>
       </c>
       <c r="N5" t="n">
-        <v>-170.94875</v>
+        <v>-113.83375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.16875</v>
+        <v>-0.16375</v>
       </c>
       <c r="N6" t="n">
-        <v>-93.2775</v>
+        <v>-73.09125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0275</v>
+        <v>-0.02874999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>-52.25125</v>
+        <v>-39.90375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05125</v>
+        <v>0.06000000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-19.435</v>
+        <v>-8.93</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>-0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.07625000000000003</v>
       </c>
       <c r="N9" t="n">
         <v>10.3525</v>
@@ -9322,6 +9322,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>8291</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-150.48</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-414.81%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-0.36875</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-682.06625</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X71" t="n">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>84.04000000000002</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.3583489681050658</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>456.92</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.7522555153111623</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
